--- a/artfynd/A 20926-2025 artfynd.xlsx
+++ b/artfynd/A 20926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436305</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2025 artfynd.xlsx
+++ b/artfynd/A 20926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436305</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2025 artfynd.xlsx
+++ b/artfynd/A 20926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436305</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2025 artfynd.xlsx
+++ b/artfynd/A 20926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436305</v>
       </c>
       <c r="B2" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2025 artfynd.xlsx
+++ b/artfynd/A 20926-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436305</v>
       </c>
       <c r="B2" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
